--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T443"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29592,6 +29592,138 @@
         <v>277.5</v>
       </c>
       <c r="T443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>290.43</v>
+      </c>
+      <c r="C444" t="n">
+        <v>309.19</v>
+      </c>
+      <c r="D444" t="n">
+        <v>293.06</v>
+      </c>
+      <c r="E444" t="n">
+        <v>292.08</v>
+      </c>
+      <c r="F444" t="n">
+        <v>296.09</v>
+      </c>
+      <c r="G444" t="n">
+        <v>293.78</v>
+      </c>
+      <c r="H444" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="I444" t="n">
+        <v>295.51</v>
+      </c>
+      <c r="J444" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="K444" t="n">
+        <v>288.84</v>
+      </c>
+      <c r="L444" t="n">
+        <v>290.29</v>
+      </c>
+      <c r="M444" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="N444" t="n">
+        <v>272.57</v>
+      </c>
+      <c r="O444" t="n">
+        <v>279.06</v>
+      </c>
+      <c r="P444" t="n">
+        <v>271.73</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>271.51</v>
+      </c>
+      <c r="R444" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="S444" t="n">
+        <v>275.58</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>290.77</v>
+      </c>
+      <c r="C445" t="n">
+        <v>304.66</v>
+      </c>
+      <c r="D445" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="E445" t="n">
+        <v>290.88</v>
+      </c>
+      <c r="F445" t="n">
+        <v>293.98</v>
+      </c>
+      <c r="G445" t="n">
+        <v>289.77</v>
+      </c>
+      <c r="H445" t="n">
+        <v>291.06</v>
+      </c>
+      <c r="I445" t="n">
+        <v>290.11</v>
+      </c>
+      <c r="J445" t="n">
+        <v>288.09</v>
+      </c>
+      <c r="K445" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="L445" t="n">
+        <v>284.13</v>
+      </c>
+      <c r="M445" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="N445" t="n">
+        <v>267.91</v>
+      </c>
+      <c r="O445" t="n">
+        <v>273.74</v>
+      </c>
+      <c r="P445" t="n">
+        <v>269.97</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>270.91</v>
+      </c>
+      <c r="R445" t="n">
+        <v>272.67</v>
+      </c>
+      <c r="S445" t="n">
+        <v>275.51</v>
+      </c>
+      <c r="T445" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29608,7 +29740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34831,6 +34963,26 @@
       </c>
       <c r="B522" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -34999,28 +35151,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6219595478209763</v>
+        <v>-0.6243206289261856</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07259439122329536</v>
+        <v>0.07372915523178147</v>
       </c>
       <c r="M2" t="n">
-        <v>14.4995117250113</v>
+        <v>14.44686862816012</v>
       </c>
       <c r="N2" t="n">
-        <v>305.1298043493712</v>
+        <v>303.7769213593351</v>
       </c>
       <c r="O2" t="n">
-        <v>17.46796508896704</v>
+        <v>17.42919738138664</v>
       </c>
       <c r="P2" t="n">
-        <v>310.1867763299527</v>
+        <v>310.210717349399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35077,28 +35229,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.559682607151997</v>
+        <v>-0.5443476069710984</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07163313378163461</v>
+        <v>0.06820529868548153</v>
       </c>
       <c r="M3" t="n">
-        <v>13.22236414355283</v>
+        <v>13.24566696010365</v>
       </c>
       <c r="N3" t="n">
-        <v>257.4434183205068</v>
+        <v>257.9162137664077</v>
       </c>
       <c r="O3" t="n">
-        <v>16.04504341909073</v>
+        <v>16.05977004089435</v>
       </c>
       <c r="P3" t="n">
-        <v>302.9476705673875</v>
+        <v>302.7955546682575</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35155,28 +35307,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8643087705231584</v>
+        <v>-0.8534067971683964</v>
       </c>
       <c r="J4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1205041129358758</v>
+        <v>0.1185512425839497</v>
       </c>
       <c r="M4" t="n">
-        <v>11.27891000119174</v>
+        <v>11.28155519970061</v>
       </c>
       <c r="N4" t="n">
-        <v>345.0346924773353</v>
+        <v>344.2975994889841</v>
       </c>
       <c r="O4" t="n">
-        <v>18.57510948762713</v>
+        <v>18.55525800114307</v>
       </c>
       <c r="P4" t="n">
-        <v>302.5644340347074</v>
+        <v>302.4562598047809</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35233,28 +35385,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.075238456610734</v>
+        <v>-1.060889219934877</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2532451712142075</v>
+        <v>0.2487096938613609</v>
       </c>
       <c r="M5" t="n">
-        <v>11.45884065717409</v>
+        <v>11.47468092003248</v>
       </c>
       <c r="N5" t="n">
-        <v>212.1625634041675</v>
+        <v>212.5817934020057</v>
       </c>
       <c r="O5" t="n">
-        <v>14.56580115902203</v>
+        <v>14.58018495774336</v>
       </c>
       <c r="P5" t="n">
-        <v>302.8200740429963</v>
+        <v>302.6755888989738</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35311,28 +35463,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.098652424047525</v>
+        <v>-1.080845509955707</v>
       </c>
       <c r="J6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2355600071243954</v>
+        <v>0.2297954777905425</v>
       </c>
       <c r="M6" t="n">
-        <v>12.69306760606248</v>
+        <v>12.73635127005974</v>
       </c>
       <c r="N6" t="n">
-        <v>247.8879748237153</v>
+        <v>248.9560426647946</v>
       </c>
       <c r="O6" t="n">
-        <v>15.74445854336424</v>
+        <v>15.77834093511718</v>
       </c>
       <c r="P6" t="n">
-        <v>302.4082096817797</v>
+        <v>302.2315219872896</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35389,28 +35541,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.153423353475387</v>
+        <v>-1.134803912387818</v>
       </c>
       <c r="J7" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2156734036270223</v>
+        <v>0.2104440671409403</v>
       </c>
       <c r="M7" t="n">
-        <v>14.00771578523943</v>
+        <v>14.05782318383124</v>
       </c>
       <c r="N7" t="n">
-        <v>306.8696622311181</v>
+        <v>307.8910610997709</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5176956883923</v>
+        <v>17.54682481532687</v>
       </c>
       <c r="P7" t="n">
-        <v>299.6085003556611</v>
+        <v>299.4239811638994</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35467,28 +35619,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.263104063481344</v>
+        <v>-1.240983929912623</v>
       </c>
       <c r="J8" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.195341230302593</v>
+        <v>0.1900095725932088</v>
       </c>
       <c r="M8" t="n">
-        <v>15.67528595389745</v>
+        <v>15.73711905155347</v>
       </c>
       <c r="N8" t="n">
-        <v>416.842718359798</v>
+        <v>418.3559378710432</v>
       </c>
       <c r="O8" t="n">
-        <v>20.41672643593478</v>
+        <v>20.45375119314409</v>
       </c>
       <c r="P8" t="n">
-        <v>299.786934223415</v>
+        <v>299.5677230232674</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35545,28 +35697,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8524452695718405</v>
+        <v>-0.8321390360205361</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K9" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1005048121935331</v>
+        <v>0.09642310602056436</v>
       </c>
       <c r="M9" t="n">
-        <v>16.24361205894397</v>
+        <v>16.29989940578951</v>
       </c>
       <c r="N9" t="n">
-        <v>412.4973118626701</v>
+        <v>413.5090390792074</v>
       </c>
       <c r="O9" t="n">
-        <v>20.31002983411571</v>
+        <v>20.33492166395552</v>
       </c>
       <c r="P9" t="n">
-        <v>290.4567011611323</v>
+        <v>290.2554660886377</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35623,28 +35775,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8613262191404294</v>
+        <v>-0.8428395896998833</v>
       </c>
       <c r="J10" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1292859566919495</v>
+        <v>0.1246610192119662</v>
       </c>
       <c r="M10" t="n">
-        <v>13.97584911424569</v>
+        <v>14.01819992506268</v>
       </c>
       <c r="N10" t="n">
-        <v>319.4630567305057</v>
+        <v>320.4131001604324</v>
       </c>
       <c r="O10" t="n">
-        <v>17.87352949840925</v>
+        <v>17.90008659645065</v>
       </c>
       <c r="P10" t="n">
-        <v>290.8603755044201</v>
+        <v>290.6779262771155</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35701,28 +35853,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9149850993925395</v>
+        <v>-0.8948891444741426</v>
       </c>
       <c r="J11" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K11" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1302216955007064</v>
+        <v>0.1254076942882063</v>
       </c>
       <c r="M11" t="n">
-        <v>14.61489615276526</v>
+        <v>14.65004632056144</v>
       </c>
       <c r="N11" t="n">
-        <v>354.5054201833169</v>
+        <v>355.7382956239718</v>
       </c>
       <c r="O11" t="n">
-        <v>18.82831432134372</v>
+        <v>18.86102583699974</v>
       </c>
       <c r="P11" t="n">
-        <v>284.8944918547382</v>
+        <v>284.6953774864403</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35779,28 +35931,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6429388815733483</v>
+        <v>-0.6193375109153747</v>
       </c>
       <c r="J12" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K12" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05218053936886646</v>
+        <v>0.04865426155427677</v>
       </c>
       <c r="M12" t="n">
-        <v>17.3512992209461</v>
+        <v>17.3946384389901</v>
       </c>
       <c r="N12" t="n">
-        <v>467.0735255822227</v>
+        <v>468.7389243972183</v>
       </c>
       <c r="O12" t="n">
-        <v>21.61188389711139</v>
+        <v>21.65037931301016</v>
       </c>
       <c r="P12" t="n">
-        <v>275.5968012485783</v>
+        <v>275.3586726331519</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35857,28 +36009,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.458060533695699</v>
+        <v>-0.4313290274703476</v>
       </c>
       <c r="J13" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K13" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02580021797757237</v>
+        <v>0.02293183138897448</v>
       </c>
       <c r="M13" t="n">
-        <v>18.20541248819773</v>
+        <v>18.26890584149548</v>
       </c>
       <c r="N13" t="n">
-        <v>507.052781629311</v>
+        <v>509.7066953316241</v>
       </c>
       <c r="O13" t="n">
-        <v>22.51783252511909</v>
+        <v>22.57668477282757</v>
       </c>
       <c r="P13" t="n">
-        <v>273.5148599815826</v>
+        <v>273.2515669910196</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35935,28 +36087,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.323853432883972</v>
+        <v>-1.306162225788157</v>
       </c>
       <c r="J14" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K14" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2022080532958609</v>
+        <v>0.1985679116479122</v>
       </c>
       <c r="M14" t="n">
-        <v>16.57404722895564</v>
+        <v>16.59455599478103</v>
       </c>
       <c r="N14" t="n">
-        <v>440.1996492328807</v>
+        <v>440.3975752674164</v>
       </c>
       <c r="O14" t="n">
-        <v>20.98093537554703</v>
+        <v>20.98565165219837</v>
       </c>
       <c r="P14" t="n">
-        <v>283.7957262265242</v>
+        <v>283.6206004399302</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36013,28 +36165,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3215044788518018</v>
+        <v>-0.3063377227169194</v>
       </c>
       <c r="J15" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K15" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02274477208227899</v>
+        <v>0.02076511023323035</v>
       </c>
       <c r="M15" t="n">
-        <v>13.32024001857988</v>
+        <v>13.35932018423616</v>
       </c>
       <c r="N15" t="n">
-        <v>278.2463654748751</v>
+        <v>278.5537379597673</v>
       </c>
       <c r="O15" t="n">
-        <v>16.68071837406516</v>
+        <v>16.68992923771001</v>
       </c>
       <c r="P15" t="n">
-        <v>266.5264299844795</v>
+        <v>266.374075699622</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36091,28 +36243,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.90216525045133</v>
+        <v>-0.890311774270623</v>
       </c>
       <c r="J16" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K16" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1899438919671074</v>
+        <v>0.1866435009535973</v>
       </c>
       <c r="M16" t="n">
-        <v>11.40534827788166</v>
+        <v>11.43369749333038</v>
       </c>
       <c r="N16" t="n">
-        <v>219.488530421483</v>
+        <v>219.4542244649527</v>
       </c>
       <c r="O16" t="n">
-        <v>14.81514530544615</v>
+        <v>14.81398745999715</v>
       </c>
       <c r="P16" t="n">
-        <v>280.4598483691184</v>
+        <v>280.3420297746659</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36169,28 +36321,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6981351196617247</v>
+        <v>-0.6891116693425542</v>
       </c>
       <c r="J17" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K17" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1466103423599716</v>
+        <v>0.144139732970177</v>
       </c>
       <c r="M17" t="n">
-        <v>9.65744261320665</v>
+        <v>9.673690647315789</v>
       </c>
       <c r="N17" t="n">
-        <v>177.0553222402708</v>
+        <v>176.8004430464955</v>
       </c>
       <c r="O17" t="n">
-        <v>13.30621367032225</v>
+        <v>13.29663277098738</v>
       </c>
       <c r="P17" t="n">
-        <v>278.9004684788411</v>
+        <v>278.8097528076299</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36247,28 +36399,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8435240935476738</v>
+        <v>-0.8347307217983972</v>
       </c>
       <c r="J18" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K18" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3362945041858008</v>
+        <v>0.3323536529034679</v>
       </c>
       <c r="M18" t="n">
-        <v>6.805521614683967</v>
+        <v>6.820292352721133</v>
       </c>
       <c r="N18" t="n">
-        <v>88.30496206284604</v>
+        <v>88.43342510293463</v>
       </c>
       <c r="O18" t="n">
-        <v>9.397071994129131</v>
+        <v>9.403904779554855</v>
       </c>
       <c r="P18" t="n">
-        <v>284.7033423228157</v>
+        <v>284.615622776766</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36325,28 +36477,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.131875207116671</v>
+        <v>-1.122317337927762</v>
       </c>
       <c r="J19" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K19" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4325921197741149</v>
+        <v>0.4292494444366549</v>
       </c>
       <c r="M19" t="n">
-        <v>8.300678764384186</v>
+        <v>8.303264881177189</v>
       </c>
       <c r="N19" t="n">
-        <v>105.6691792363389</v>
+        <v>105.8145952477995</v>
       </c>
       <c r="O19" t="n">
-        <v>10.27955150949393</v>
+        <v>10.28662214955908</v>
       </c>
       <c r="P19" t="n">
-        <v>294.1365557232884</v>
+        <v>294.0412097015175</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36384,7 +36536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T443"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81357,6 +81509,210 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-35.396886599759746,173.23967588613647</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-35.39645248660198,173.23892416351643</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-35.395808903604866,173.2384591022749</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-35.39525627168045,173.23786956635732</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-35.39473359376053,173.2372390322562</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-35.394172969723634,173.23666042369425</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-35.39363743667445,173.23604747210027</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-35.39308983286475,173.23545103472628</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-35.392529858278365,173.23487152221065</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-35.391956252351065,173.23431065971826</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-35.39141818299134,173.2337011588788</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-35.390911087174466,173.23304926419505</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-35.390218244087,173.23265156794565</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-35.38971042064069,173.23200065918286</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-35.38911962767549,173.23146329275752</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-35.38857151459529,173.23086751198144</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-35.38803456384744,173.23025644995926</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-35.38750235184481,173.229638897621</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-35.39688864099892,173.23967309264222</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-35.39642529025075,173.23896138269055</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-35.39580698245559,173.23846173143008</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-35.39524906740074,173.23787942565565</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-35.3947209262942,173.2372563681429</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-35.39414889563055,173.23669336997395</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-35.393609880665835,173.2360851835657</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-35.39305741416921,173.23549540101095</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-35.39249852033497,173.23491440946884</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-35.39191338797088,173.23436932136556</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-35.391381202123604,173.2337517687804</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-35.39088016988203,173.23309157595415</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-35.390190268497626,173.23268985366673</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-35.38967848299942,173.23204436724544</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-35.38910906187937,173.23147775250962</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-35.388567912635,173.23087244142692</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-35.38803168229207,173.23026039350404</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-35.38750193161991,173.22963947271967</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29726,6 +29726,204 @@
       <c r="T445" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>291.36</v>
+      </c>
+      <c r="C446" t="n">
+        <v>301.61</v>
+      </c>
+      <c r="D446" t="n">
+        <v>291.46</v>
+      </c>
+      <c r="E446" t="n">
+        <v>289.47</v>
+      </c>
+      <c r="F446" t="n">
+        <v>292.72</v>
+      </c>
+      <c r="G446" t="n">
+        <v>287.64</v>
+      </c>
+      <c r="H446" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="I446" t="n">
+        <v>287.58</v>
+      </c>
+      <c r="J446" t="n">
+        <v>285.53</v>
+      </c>
+      <c r="K446" t="n">
+        <v>279.54</v>
+      </c>
+      <c r="L446" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="M446" t="n">
+        <v>287.65</v>
+      </c>
+      <c r="N446" t="n">
+        <v>267.91</v>
+      </c>
+      <c r="O446" t="n">
+        <v>270.04</v>
+      </c>
+      <c r="P446" t="n">
+        <v>267.3</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>269.48</v>
+      </c>
+      <c r="R446" t="n">
+        <v>271.7</v>
+      </c>
+      <c r="S446" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>291.55</v>
+      </c>
+      <c r="C447" t="n">
+        <v>300.14</v>
+      </c>
+      <c r="D447" t="n">
+        <v>291.41</v>
+      </c>
+      <c r="E447" t="n">
+        <v>288.56</v>
+      </c>
+      <c r="F447" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="G447" t="n">
+        <v>287.08</v>
+      </c>
+      <c r="H447" t="n">
+        <v>287.37</v>
+      </c>
+      <c r="I447" t="n">
+        <v>285.16</v>
+      </c>
+      <c r="J447" t="n">
+        <v>283.87</v>
+      </c>
+      <c r="K447" t="n">
+        <v>278.89</v>
+      </c>
+      <c r="L447" t="n">
+        <v>280.59</v>
+      </c>
+      <c r="M447" t="n">
+        <v>285.39</v>
+      </c>
+      <c r="N447" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="O447" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="P447" t="n">
+        <v>266.36</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="R447" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="S447" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>291.55</v>
+      </c>
+      <c r="C448" t="n">
+        <v>300.14</v>
+      </c>
+      <c r="D448" t="n">
+        <v>291.41</v>
+      </c>
+      <c r="E448" t="n">
+        <v>288.56</v>
+      </c>
+      <c r="F448" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="G448" t="n">
+        <v>287.08</v>
+      </c>
+      <c r="H448" t="n">
+        <v>287.37</v>
+      </c>
+      <c r="I448" t="n">
+        <v>285.16</v>
+      </c>
+      <c r="J448" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="K448" t="n">
+        <v>278.89</v>
+      </c>
+      <c r="L448" t="n">
+        <v>280.59</v>
+      </c>
+      <c r="M448" t="n">
+        <v>285.39</v>
+      </c>
+      <c r="N448" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="O448" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="P448" t="n">
+        <v>266.36</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="R448" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="S448" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29740,7 +29938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34983,6 +35181,46 @@
       </c>
       <c r="B524" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -35151,28 +35389,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6243206289261856</v>
+        <v>-0.6266171805165602</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07372915523178147</v>
+        <v>0.07518326271949149</v>
       </c>
       <c r="M2" t="n">
-        <v>14.44686862816012</v>
+        <v>14.36166715214147</v>
       </c>
       <c r="N2" t="n">
-        <v>303.7769213593351</v>
+        <v>301.738809713876</v>
       </c>
       <c r="O2" t="n">
-        <v>17.42919738138664</v>
+        <v>17.37063066540406</v>
       </c>
       <c r="P2" t="n">
-        <v>310.210717349399</v>
+        <v>310.2341105218783</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35229,28 +35467,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5443476069710984</v>
+        <v>-0.5293928718991266</v>
       </c>
       <c r="J3" t="n">
+        <v>447</v>
+      </c>
+      <c r="K3" t="n">
         <v>444</v>
       </c>
-      <c r="K3" t="n">
-        <v>441</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06820529868548153</v>
+        <v>0.06533844852309822</v>
       </c>
       <c r="M3" t="n">
-        <v>13.24566696010365</v>
+        <v>13.23732543155834</v>
       </c>
       <c r="N3" t="n">
-        <v>257.9162137664077</v>
+        <v>257.2131700487699</v>
       </c>
       <c r="O3" t="n">
-        <v>16.05977004089435</v>
+        <v>16.03786675492629</v>
       </c>
       <c r="P3" t="n">
-        <v>302.7955546682575</v>
+        <v>302.646515865103</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35307,28 +35545,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8534067971683964</v>
+        <v>-0.839126182898369</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1185512425839497</v>
+        <v>0.1161913406185188</v>
       </c>
       <c r="M4" t="n">
-        <v>11.28155519970061</v>
+        <v>11.27702481768968</v>
       </c>
       <c r="N4" t="n">
-        <v>344.2975994889841</v>
+        <v>342.9315167308924</v>
       </c>
       <c r="O4" t="n">
-        <v>18.55525800114307</v>
+        <v>18.51841021067663</v>
       </c>
       <c r="P4" t="n">
-        <v>302.4562598047809</v>
+        <v>302.3138943063083</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35385,28 +35623,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.060889219934877</v>
+        <v>-1.042966784133307</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2487096938613609</v>
+        <v>0.2436780608522853</v>
       </c>
       <c r="M5" t="n">
-        <v>11.47468092003248</v>
+        <v>11.48186453755551</v>
       </c>
       <c r="N5" t="n">
-        <v>212.5817934020057</v>
+        <v>212.5962899383336</v>
       </c>
       <c r="O5" t="n">
-        <v>14.58018495774336</v>
+        <v>14.58068208069614</v>
       </c>
       <c r="P5" t="n">
-        <v>302.6755888989738</v>
+        <v>302.4942905765409</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35463,28 +35701,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.080845509955707</v>
+        <v>-1.058035380575105</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2297954777905425</v>
+        <v>0.2230291774056729</v>
       </c>
       <c r="M6" t="n">
-        <v>12.73635127005974</v>
+        <v>12.7786354294272</v>
       </c>
       <c r="N6" t="n">
-        <v>248.9560426647946</v>
+        <v>249.6961089209212</v>
       </c>
       <c r="O6" t="n">
-        <v>15.77834093511718</v>
+        <v>15.80177549900394</v>
       </c>
       <c r="P6" t="n">
-        <v>302.2315219872896</v>
+        <v>302.0041283104272</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35541,28 +35779,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.134803912387818</v>
+        <v>-1.112826318964669</v>
       </c>
       <c r="J7" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2104440671409403</v>
+        <v>0.205062999764152</v>
       </c>
       <c r="M7" t="n">
-        <v>14.05782318383124</v>
+        <v>14.09616744591914</v>
       </c>
       <c r="N7" t="n">
-        <v>307.8910610997709</v>
+        <v>308.0631228261133</v>
       </c>
       <c r="O7" t="n">
-        <v>17.54682481532687</v>
+        <v>17.55172706106477</v>
       </c>
       <c r="P7" t="n">
-        <v>299.4239811638994</v>
+        <v>299.2051555154706</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35619,28 +35857,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.240983929912623</v>
+        <v>-1.215237581275847</v>
       </c>
       <c r="J8" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1900095725932088</v>
+        <v>0.1845929680954033</v>
       </c>
       <c r="M8" t="n">
-        <v>15.73711905155347</v>
+        <v>15.79271426922282</v>
       </c>
       <c r="N8" t="n">
-        <v>418.3559378710432</v>
+        <v>418.6211958330232</v>
       </c>
       <c r="O8" t="n">
-        <v>20.45375119314409</v>
+        <v>20.46023450092943</v>
       </c>
       <c r="P8" t="n">
-        <v>299.5677230232674</v>
+        <v>299.3113748958389</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35697,28 +35935,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8321390360205361</v>
+        <v>-0.8105143497163169</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K9" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09642310602056436</v>
+        <v>0.09263788299557041</v>
       </c>
       <c r="M9" t="n">
-        <v>16.29989940578951</v>
+        <v>16.32673674336656</v>
       </c>
       <c r="N9" t="n">
-        <v>413.5090390792074</v>
+        <v>412.9076879070394</v>
       </c>
       <c r="O9" t="n">
-        <v>20.33492166395552</v>
+        <v>20.32013011540624</v>
       </c>
       <c r="P9" t="n">
-        <v>290.2554660886377</v>
+        <v>290.0401647535077</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35775,28 +36013,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8428395896998833</v>
+        <v>-0.8233684322996827</v>
       </c>
       <c r="J10" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K10" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1246610192119662</v>
+        <v>0.1205091261976703</v>
       </c>
       <c r="M10" t="n">
-        <v>14.01819992506268</v>
+        <v>14.03603909356488</v>
       </c>
       <c r="N10" t="n">
-        <v>320.4131001604324</v>
+        <v>320.0189343922058</v>
       </c>
       <c r="O10" t="n">
-        <v>17.90008659645065</v>
+        <v>17.88907304452094</v>
       </c>
       <c r="P10" t="n">
-        <v>290.6779262771155</v>
+        <v>290.4848494207322</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35853,28 +36091,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8948891444741426</v>
+        <v>-0.8727713195740188</v>
       </c>
       <c r="J11" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K11" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1254076942882063</v>
+        <v>0.1207994955223933</v>
       </c>
       <c r="M11" t="n">
-        <v>14.65004632056144</v>
+        <v>14.66421476263085</v>
       </c>
       <c r="N11" t="n">
-        <v>355.7382956239718</v>
+        <v>355.6119891836345</v>
       </c>
       <c r="O11" t="n">
-        <v>18.86102583699974</v>
+        <v>18.8576771948094</v>
       </c>
       <c r="P11" t="n">
-        <v>284.6953774864403</v>
+        <v>284.4751982289628</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35931,28 +36169,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6193375109153747</v>
+        <v>-0.5926128245787899</v>
       </c>
       <c r="J12" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04865426155427677</v>
+        <v>0.04502301227520944</v>
       </c>
       <c r="M12" t="n">
-        <v>17.3946384389901</v>
+        <v>17.41590530652472</v>
       </c>
       <c r="N12" t="n">
-        <v>468.7389243972183</v>
+        <v>468.7975698276457</v>
       </c>
       <c r="O12" t="n">
-        <v>21.65037931301016</v>
+        <v>21.65173364485268</v>
       </c>
       <c r="P12" t="n">
-        <v>275.3586726331519</v>
+        <v>275.0877738494061</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36009,28 +36247,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4313290274703476</v>
+        <v>-0.4020022510959227</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K13" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02293183138897448</v>
+        <v>0.02009563201206555</v>
       </c>
       <c r="M13" t="n">
-        <v>18.26890584149548</v>
+        <v>18.31092568681598</v>
       </c>
       <c r="N13" t="n">
-        <v>509.7066953316241</v>
+        <v>510.2540440964098</v>
       </c>
       <c r="O13" t="n">
-        <v>22.57668477282757</v>
+        <v>22.58880351183767</v>
       </c>
       <c r="P13" t="n">
-        <v>273.2515669910196</v>
+        <v>272.961342617994</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36087,28 +36325,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.306162225788157</v>
+        <v>-1.285435781579529</v>
       </c>
       <c r="J14" t="n">
+        <v>447</v>
+      </c>
+      <c r="K14" t="n">
         <v>444</v>
       </c>
-      <c r="K14" t="n">
-        <v>441</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1985679116479122</v>
+        <v>0.1949473616963945</v>
       </c>
       <c r="M14" t="n">
-        <v>16.59455599478103</v>
+        <v>16.59372991761643</v>
       </c>
       <c r="N14" t="n">
-        <v>440.3975752674164</v>
+        <v>439.4436174264931</v>
       </c>
       <c r="O14" t="n">
-        <v>20.98565165219837</v>
+        <v>20.96291051897358</v>
       </c>
       <c r="P14" t="n">
-        <v>283.6206004399302</v>
+        <v>283.414467832387</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36165,28 +36403,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3063377227169194</v>
+        <v>-0.2931046274295921</v>
       </c>
       <c r="J15" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K15" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02076511023323035</v>
+        <v>0.01924863876379423</v>
       </c>
       <c r="M15" t="n">
-        <v>13.35932018423616</v>
+        <v>13.35564720069088</v>
       </c>
       <c r="N15" t="n">
-        <v>278.5537379597673</v>
+        <v>277.4467459718516</v>
       </c>
       <c r="O15" t="n">
-        <v>16.68992923771001</v>
+        <v>16.65673275200907</v>
       </c>
       <c r="P15" t="n">
-        <v>266.374075699622</v>
+        <v>266.240526864937</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36243,28 +36481,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.890311774270623</v>
+        <v>-0.8778951663493111</v>
       </c>
       <c r="J16" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K16" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866435009535973</v>
+        <v>0.1839946810013456</v>
       </c>
       <c r="M16" t="n">
-        <v>11.43369749333038</v>
+        <v>11.43967926228234</v>
       </c>
       <c r="N16" t="n">
-        <v>219.4542244649527</v>
+        <v>218.679172189072</v>
       </c>
       <c r="O16" t="n">
-        <v>14.81398745999715</v>
+        <v>14.78780484686865</v>
       </c>
       <c r="P16" t="n">
-        <v>280.3420297746659</v>
+        <v>280.2180365256751</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36321,28 +36559,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6891116693425542</v>
+        <v>-0.6776635358334916</v>
       </c>
       <c r="J17" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K17" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L17" t="n">
-        <v>0.144139732970177</v>
+        <v>0.1413127987148124</v>
       </c>
       <c r="M17" t="n">
-        <v>9.673690647315789</v>
+        <v>9.683398616662192</v>
       </c>
       <c r="N17" t="n">
-        <v>176.8004430464955</v>
+        <v>176.1993187434039</v>
       </c>
       <c r="O17" t="n">
-        <v>13.29663277098738</v>
+        <v>13.27400914356337</v>
       </c>
       <c r="P17" t="n">
-        <v>278.8097528076299</v>
+        <v>278.6941217542519</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36399,28 +36637,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8347307217983972</v>
+        <v>-0.8226749779747525</v>
       </c>
       <c r="J18" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K18" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3323536529034679</v>
+        <v>0.3272894048949977</v>
       </c>
       <c r="M18" t="n">
-        <v>6.820292352721133</v>
+        <v>6.837973526687105</v>
       </c>
       <c r="N18" t="n">
-        <v>88.43342510293463</v>
+        <v>88.50666312027658</v>
       </c>
       <c r="O18" t="n">
-        <v>9.403904779554855</v>
+        <v>9.407797995294999</v>
       </c>
       <c r="P18" t="n">
-        <v>284.615622776766</v>
+        <v>284.4947918345746</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36477,28 +36715,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.122317337927762</v>
+        <v>-1.108539905957642</v>
       </c>
       <c r="J19" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K19" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4292494444366549</v>
+        <v>0.4245489050776613</v>
       </c>
       <c r="M19" t="n">
-        <v>8.303264881177189</v>
+        <v>8.306374318269247</v>
       </c>
       <c r="N19" t="n">
-        <v>105.8145952477995</v>
+        <v>105.9757328435838</v>
       </c>
       <c r="O19" t="n">
-        <v>10.28662214955908</v>
+        <v>10.29445155623085</v>
       </c>
       <c r="P19" t="n">
-        <v>294.0412097015175</v>
+        <v>293.9031220251534</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36536,7 +36774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81713,6 +81951,312 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-35.39689218314904,173.23966824510777</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-35.396406979235174,173.2389864419438</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-35.39579929785788,173.23847224804953</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-35.39524060237107,173.23789101032895</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-35.39471336183444,173.237266720376</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-35.394136108141026,173.23671087010956</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-35.393593911383114,173.2361070381287</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-35.39304222540438,173.2355161874247</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-35.39248315152956,173.23493544228828</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-35.391900420589735,173.23438706773405</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-35.39136247154611,173.2337774023493</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-35.39085555610461,173.2331252610208</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-35.390190268497626,173.23268985366673</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-35.38965627072078,173.23207476568967</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-35.389093033083064,173.2314996886036</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-35.38855932796213,173.23088418993683</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-35.388025859148556,173.2302683627499</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-35.38749676885652,173.22964653821705</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-35.39689332384143,173.23966668403722</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-35.39639815392417,173.23899851967826</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-35.39579899767826,173.23847265885493</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-35.39523513912437,173.2378984869608</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-35.394708919214814,173.23727280025804</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-35.39413274617154,173.23671547108324</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-35.39358772778761,173.23611550060755</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-35.393027697017295,173.23553607007406</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-35.39247318581784,173.23494908075287</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-35.39189651836805,173.23439240807528</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-35.391359950121796,173.23378085302113</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-35.39084198850622,173.23314382887804</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-35.39017129791938,173.23271581564276</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-35.38964702560795,173.23208741801022</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-35.389087389985285,173.23150741142115</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-35.388561309040576,173.23088147874245</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-35.38803006141712,173.23026261174783</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>-35.38750241187694,173.22963881546406</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-35.39689332384143,173.23966668403722</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-35.39639815392417,173.23899851967826</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-35.39579899767826,173.23847265885493</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-35.39523513912437,173.2378984869608</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-35.394708919214814,173.23727280025804</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-35.39413274617154,173.23671547108324</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-35.39358772778761,173.23611550060755</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-35.393027697017295,173.23553607007406</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-35.39247078444129,173.23495236712938</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-35.39189651836805,173.23439240807528</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-35.391359950121796,173.23378085302113</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-35.39084198850622,173.23314382887804</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-35.39017129791938,173.23271581564276</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-35.38964702560795,173.23208741801022</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-35.389087389985285,173.23150741142115</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-35.388561309040576,173.23088147874245</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-35.38803006141712,173.23026261174783</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>-35.38750241187694,173.22963881546406</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T448"/>
+  <dimension ref="A1:T449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29871,10 +29871,10 @@
         <v>291.55</v>
       </c>
       <c r="C448" t="n">
-        <v>300.14</v>
+        <v>321.75</v>
       </c>
       <c r="D448" t="n">
-        <v>291.41</v>
+        <v>306.29</v>
       </c>
       <c r="E448" t="n">
         <v>288.56</v>
@@ -29895,10 +29895,10 @@
         <v>283.47</v>
       </c>
       <c r="K448" t="n">
-        <v>278.89</v>
+        <v>286.67</v>
       </c>
       <c r="L448" t="n">
-        <v>280.59</v>
+        <v>289.82</v>
       </c>
       <c r="M448" t="n">
         <v>285.39</v>
@@ -29922,6 +29922,72 @@
         <v>275.59</v>
       </c>
       <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>308.85</v>
+      </c>
+      <c r="C449" t="n">
+        <v>321.75</v>
+      </c>
+      <c r="D449" t="n">
+        <v>306.29</v>
+      </c>
+      <c r="E449" t="n">
+        <v>286.94</v>
+      </c>
+      <c r="F449" t="n">
+        <v>290.09</v>
+      </c>
+      <c r="G449" t="n">
+        <v>286.37</v>
+      </c>
+      <c r="H449" t="n">
+        <v>301.57</v>
+      </c>
+      <c r="I449" t="n">
+        <v>303.34</v>
+      </c>
+      <c r="J449" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="K449" t="n">
+        <v>286.67</v>
+      </c>
+      <c r="L449" t="n">
+        <v>289.82</v>
+      </c>
+      <c r="M449" t="n">
+        <v>285.39</v>
+      </c>
+      <c r="N449" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="O449" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="P449" t="n">
+        <v>266.36</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>269.81</v>
+      </c>
+      <c r="R449" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="S449" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="T449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29938,7 +30004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35221,6 +35287,26 @@
       </c>
       <c r="B528" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -35389,28 +35475,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6266171805165602</v>
+        <v>-0.6203144355986081</v>
       </c>
       <c r="J2" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07518326271949149</v>
+        <v>0.07397949832037198</v>
       </c>
       <c r="M2" t="n">
-        <v>14.36166715214147</v>
+        <v>14.36396904896612</v>
       </c>
       <c r="N2" t="n">
-        <v>301.738809713876</v>
+        <v>301.5999434857555</v>
       </c>
       <c r="O2" t="n">
-        <v>17.37063066540406</v>
+        <v>17.36663304978128</v>
       </c>
       <c r="P2" t="n">
-        <v>310.2341105218783</v>
+        <v>310.1697210792159</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35467,28 +35553,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5293928718991266</v>
+        <v>-0.5075423212223541</v>
       </c>
       <c r="J3" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06533844852309822</v>
+        <v>0.05961773076610233</v>
       </c>
       <c r="M3" t="n">
-        <v>13.23732543155834</v>
+        <v>13.32675011258194</v>
       </c>
       <c r="N3" t="n">
-        <v>257.2131700487699</v>
+        <v>261.2902613352105</v>
       </c>
       <c r="O3" t="n">
-        <v>16.03786675492629</v>
+        <v>16.16447528796436</v>
       </c>
       <c r="P3" t="n">
-        <v>302.646515865103</v>
+        <v>302.4282861331221</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35545,28 +35631,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.839126182898369</v>
+        <v>-0.8226810220076692</v>
       </c>
       <c r="J4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1161913406185188</v>
+        <v>0.1118190438075993</v>
       </c>
       <c r="M4" t="n">
-        <v>11.27702481768968</v>
+        <v>11.33536505236474</v>
       </c>
       <c r="N4" t="n">
-        <v>342.9315167308924</v>
+        <v>344.9996488767212</v>
       </c>
       <c r="O4" t="n">
-        <v>18.51841021067663</v>
+        <v>18.57416616908337</v>
       </c>
       <c r="P4" t="n">
-        <v>302.3138943063083</v>
+        <v>302.1495967477622</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35623,28 +35709,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.042966784133307</v>
+        <v>-1.037875481697192</v>
       </c>
       <c r="J5" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2436780608522853</v>
+        <v>0.2424095429873099</v>
       </c>
       <c r="M5" t="n">
-        <v>11.48186453755551</v>
+        <v>11.4799249033696</v>
       </c>
       <c r="N5" t="n">
-        <v>212.5962899383336</v>
+        <v>212.4743957994388</v>
       </c>
       <c r="O5" t="n">
-        <v>14.58068208069614</v>
+        <v>14.5765014938235</v>
       </c>
       <c r="P5" t="n">
-        <v>302.4942905765409</v>
+        <v>302.4426378159858</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35701,28 +35787,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.058035380575105</v>
+        <v>-1.05142160940719</v>
       </c>
       <c r="J6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2230291774056729</v>
+        <v>0.2212196425279608</v>
       </c>
       <c r="M6" t="n">
-        <v>12.7786354294272</v>
+        <v>12.78780425544279</v>
       </c>
       <c r="N6" t="n">
-        <v>249.6961089209212</v>
+        <v>249.7555297446808</v>
       </c>
       <c r="O6" t="n">
-        <v>15.80177549900394</v>
+        <v>15.80365558168998</v>
       </c>
       <c r="P6" t="n">
-        <v>302.0041283104272</v>
+        <v>301.9380012418317</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35779,28 +35865,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.112826318964669</v>
+        <v>-1.105989651314503</v>
       </c>
       <c r="J7" t="n">
+        <v>448</v>
+      </c>
+      <c r="K7" t="n">
         <v>447</v>
       </c>
-      <c r="K7" t="n">
-        <v>446</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.205062999764152</v>
+        <v>0.2034488069675163</v>
       </c>
       <c r="M7" t="n">
-        <v>14.09616744591914</v>
+        <v>14.10575512121356</v>
       </c>
       <c r="N7" t="n">
-        <v>308.0631228261133</v>
+        <v>308.0345496533314</v>
       </c>
       <c r="O7" t="n">
-        <v>17.55172706106477</v>
+        <v>17.55091307178437</v>
       </c>
       <c r="P7" t="n">
-        <v>299.2051555154706</v>
+        <v>299.1368831598683</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35857,28 +35943,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.215237581275847</v>
+        <v>-1.201317940890223</v>
       </c>
       <c r="J8" t="n">
+        <v>448</v>
+      </c>
+      <c r="K8" t="n">
         <v>447</v>
       </c>
-      <c r="K8" t="n">
-        <v>446</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1845929680954033</v>
+        <v>0.1808544247754521</v>
       </c>
       <c r="M8" t="n">
-        <v>15.79271426922282</v>
+        <v>15.84626028170085</v>
       </c>
       <c r="N8" t="n">
-        <v>418.6211958330232</v>
+        <v>420.4231636133911</v>
       </c>
       <c r="O8" t="n">
-        <v>20.46023450092943</v>
+        <v>20.50422306778267</v>
       </c>
       <c r="P8" t="n">
-        <v>299.3113748958389</v>
+        <v>299.1723705318868</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35935,28 +36021,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8105143497163169</v>
+        <v>-0.7965532719387554</v>
       </c>
       <c r="J9" t="n">
+        <v>448</v>
+      </c>
+      <c r="K9" t="n">
         <v>447</v>
       </c>
-      <c r="K9" t="n">
-        <v>446</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09263788299557041</v>
+        <v>0.08958460294331105</v>
       </c>
       <c r="M9" t="n">
-        <v>16.32673674336656</v>
+        <v>16.37812012263973</v>
       </c>
       <c r="N9" t="n">
-        <v>412.9076879070394</v>
+        <v>414.7387662236142</v>
       </c>
       <c r="O9" t="n">
-        <v>20.32013011540624</v>
+        <v>20.36513604726505</v>
       </c>
       <c r="P9" t="n">
-        <v>290.0401647535077</v>
+        <v>289.90074658732</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36013,28 +36099,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8233684322996827</v>
+        <v>-0.8173263105415831</v>
       </c>
       <c r="J10" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K10" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1205091261976703</v>
+        <v>0.119261877405903</v>
       </c>
       <c r="M10" t="n">
-        <v>14.03603909356488</v>
+        <v>14.03917390075851</v>
       </c>
       <c r="N10" t="n">
-        <v>320.0189343922058</v>
+        <v>319.816879571474</v>
       </c>
       <c r="O10" t="n">
-        <v>17.88907304452094</v>
+        <v>17.88342471596182</v>
       </c>
       <c r="P10" t="n">
-        <v>290.4848494207322</v>
+        <v>290.4247534349745</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36091,28 +36177,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8727713195740188</v>
+        <v>-0.8594560140627588</v>
       </c>
       <c r="J11" t="n">
+        <v>448</v>
+      </c>
+      <c r="K11" t="n">
         <v>447</v>
       </c>
-      <c r="K11" t="n">
-        <v>446</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1207994955223933</v>
+        <v>0.1173932838715417</v>
       </c>
       <c r="M11" t="n">
-        <v>14.66421476263085</v>
+        <v>14.69964210494961</v>
       </c>
       <c r="N11" t="n">
-        <v>355.6119891836345</v>
+        <v>357.048305738663</v>
       </c>
       <c r="O11" t="n">
-        <v>18.8576771948094</v>
+        <v>18.89572188985282</v>
       </c>
       <c r="P11" t="n">
-        <v>284.4751982289628</v>
+        <v>284.3423218303217</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36169,28 +36255,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5926128245787899</v>
+        <v>-0.576517123608688</v>
       </c>
       <c r="J12" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K12" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04502301227520944</v>
+        <v>0.04262140454496011</v>
       </c>
       <c r="M12" t="n">
-        <v>17.41590530652472</v>
+        <v>17.46162196346506</v>
       </c>
       <c r="N12" t="n">
-        <v>468.7975698276457</v>
+        <v>470.9373840645894</v>
       </c>
       <c r="O12" t="n">
-        <v>21.65173364485268</v>
+        <v>21.70109177125864</v>
       </c>
       <c r="P12" t="n">
-        <v>275.0877738494061</v>
+        <v>274.9242227504957</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36247,28 +36333,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4020022510959227</v>
+        <v>-0.3927321894354611</v>
       </c>
       <c r="J13" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K13" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02009563201206555</v>
+        <v>0.0192380819065382</v>
       </c>
       <c r="M13" t="n">
-        <v>18.31092568681598</v>
+        <v>18.3223255027242</v>
       </c>
       <c r="N13" t="n">
-        <v>510.2540440964098</v>
+        <v>510.3184733584065</v>
       </c>
       <c r="O13" t="n">
-        <v>22.58880351183767</v>
+        <v>22.59022959950621</v>
       </c>
       <c r="P13" t="n">
-        <v>272.961342617994</v>
+        <v>272.8693266899534</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36325,28 +36411,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.285435781579529</v>
+        <v>-1.279063563485139</v>
       </c>
       <c r="J14" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K14" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1949473616963945</v>
+        <v>0.1938939649688428</v>
       </c>
       <c r="M14" t="n">
-        <v>16.59372991761643</v>
+        <v>16.59080339116003</v>
       </c>
       <c r="N14" t="n">
-        <v>439.4436174264931</v>
+        <v>439.033468174019</v>
       </c>
       <c r="O14" t="n">
-        <v>20.96291051897358</v>
+        <v>20.95312549893259</v>
       </c>
       <c r="P14" t="n">
-        <v>283.414467832387</v>
+        <v>283.3509001722325</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36403,28 +36489,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2931046274295921</v>
+        <v>-0.2889893986333709</v>
       </c>
       <c r="J15" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K15" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01924863876379423</v>
+        <v>0.01879053853505486</v>
       </c>
       <c r="M15" t="n">
-        <v>13.35564720069088</v>
+        <v>13.35247461218935</v>
       </c>
       <c r="N15" t="n">
-        <v>277.4467459718516</v>
+        <v>277.0494761509539</v>
       </c>
       <c r="O15" t="n">
-        <v>16.65673275200907</v>
+        <v>16.64480327762854</v>
       </c>
       <c r="P15" t="n">
-        <v>266.240526864937</v>
+        <v>266.198871164992</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36481,28 +36567,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8778951663493111</v>
+        <v>-0.8739504783946316</v>
       </c>
       <c r="J16" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K16" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1839946810013456</v>
+        <v>0.1831791139239149</v>
       </c>
       <c r="M16" t="n">
-        <v>11.43967926228234</v>
+        <v>11.44021145563894</v>
       </c>
       <c r="N16" t="n">
-        <v>218.679172189072</v>
+        <v>218.4047539173342</v>
       </c>
       <c r="O16" t="n">
-        <v>14.78780484686865</v>
+        <v>14.77852340111603</v>
       </c>
       <c r="P16" t="n">
-        <v>280.2180365256751</v>
+        <v>280.1785271533188</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36559,28 +36645,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6776635358334916</v>
+        <v>-0.6738710114343078</v>
       </c>
       <c r="J17" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K17" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1413127987148124</v>
+        <v>0.1403695288656459</v>
       </c>
       <c r="M17" t="n">
-        <v>9.683398616662192</v>
+        <v>9.686554826438337</v>
       </c>
       <c r="N17" t="n">
-        <v>176.1993187434039</v>
+        <v>176.0015973103123</v>
       </c>
       <c r="O17" t="n">
-        <v>13.27400914356337</v>
+        <v>13.26655936218251</v>
       </c>
       <c r="P17" t="n">
-        <v>278.6941217542519</v>
+        <v>278.6557048831464</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36637,28 +36723,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8226749779747525</v>
+        <v>-0.8186314852187435</v>
       </c>
       <c r="J18" t="n">
+        <v>448</v>
+      </c>
+      <c r="K18" t="n">
         <v>447</v>
       </c>
-      <c r="K18" t="n">
-        <v>446</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3272894048949977</v>
+        <v>0.3255553118370704</v>
       </c>
       <c r="M18" t="n">
-        <v>6.837973526687105</v>
+        <v>6.844492578501985</v>
       </c>
       <c r="N18" t="n">
-        <v>88.50666312027658</v>
+        <v>88.53719464790953</v>
       </c>
       <c r="O18" t="n">
-        <v>9.407797995294999</v>
+        <v>9.409420526680139</v>
       </c>
       <c r="P18" t="n">
-        <v>284.4947918345746</v>
+        <v>284.4541483311249</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36715,28 +36801,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.108539905957642</v>
+        <v>-1.10389713889719</v>
       </c>
       <c r="J19" t="n">
+        <v>448</v>
+      </c>
+      <c r="K19" t="n">
         <v>447</v>
       </c>
-      <c r="K19" t="n">
-        <v>446</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4245489050776613</v>
+        <v>0.4229159774712938</v>
       </c>
       <c r="M19" t="n">
-        <v>8.306374318269247</v>
+        <v>8.30754657004629</v>
       </c>
       <c r="N19" t="n">
-        <v>105.9757328435838</v>
+        <v>106.039943910309</v>
       </c>
       <c r="O19" t="n">
-        <v>10.29445155623085</v>
+        <v>10.29756980604206</v>
       </c>
       <c r="P19" t="n">
-        <v>293.9031220251534</v>
+        <v>293.8564548662332</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36774,7 +36860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T448"/>
+  <dimension ref="A1:T449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82168,12 +82254,12 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>-35.39639815392417,173.23899851967826</t>
+          <t>-35.39652789187777,173.23882096850102</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>-35.39579899767826,173.23847265885493</t>
+          <t>-35.39588833107039,173.23835040303155</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -82208,12 +82294,12 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>-35.39189651836805,173.23439240807528</t>
+          <t>-35.39194322494442,173.2343284882647</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>-35.391359950121796,173.23378085302113</t>
+          <t>-35.391415361399915,173.23370502035021</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -82252,6 +82338,108 @@
         </is>
       </c>
       <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-35.39699718679953,173.23952454427433</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-35.39652789187777,173.23882096850102</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-35.39588833107039,173.23835040303155</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-35.39522541334338,173.2379117970062</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-35.39469757252272,173.23728832860232</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-35.394128483674244,173.2367213044601</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-35.39367297730432,173.23599883330954</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-35.39313683994428,173.23538670355038</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-35.39247078444129,173.23495236712938</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-35.39194322494442,173.2343284882647</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-35.391415361399915,173.23370502035021</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-35.39084198850622,173.23314382887804</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-35.39017129791938,173.23271581564276</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-35.38964702560795,173.23208741801022</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-35.389087389985285,173.23150741142115</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-35.388561309040576,173.23088147874245</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-35.38803006141712,173.23026261174783</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>-35.38750241187694,173.22963881546406</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
